--- a/e2e/fixtures/assets-clean.xlsx
+++ b/e2e/fixtures/assets-clean.xlsx
@@ -79,7 +79,7 @@
     <t>Laptop</t>
   </si>
   <si>
-    <t>Dell Latitude</t>
+    <t>Standard</t>
   </si>
   <si>
     <t>TechServe PH</t>
